--- a/data/trans_dic/IMC_inf_MED_R3-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_MED_R3-Edad-trans_dic.xlsx
@@ -532,7 +532,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido (tasa de respuesta: 71,23%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido (tasa de respuesta: 79,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,28 +632,28 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.353100093784024</v>
+        <v>0.2686559845479436</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.2832274296194011</v>
+        <v>0.2572268008287363</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>0.1357179091902866</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.3587649914826891</v>
+        <v>0.3308030712115972</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.3145402589494746</v>
+        <v>0.3212775820332013</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>0.1315418755101663</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.3561614374447974</v>
+        <v>0.3024340882146896</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0.2995547830709954</v>
+        <v>0.2898026806463069</v>
       </c>
       <c r="K4" s="5" t="n">
         <v>0.133147415655342</v>
@@ -667,28 +667,28 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.2184204763422358</v>
+        <v>0.1599739288085548</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.1538181667161357</v>
+        <v>0.1502421146051437</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0.03352567606755963</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.2302864169077115</v>
+        <v>0.2309267427224705</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.1895328810031817</v>
+        <v>0.2062544886468149</v>
       </c>
       <c r="H5" s="5" t="n">
         <v>0.02003186957926138</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0.2655358624652673</v>
+        <v>0.2301399582391225</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.2022416171516465</v>
+        <v>0.1986979154969956</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>0.05067925526679805</v>
@@ -702,28 +702,28 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.5311005973805584</v>
+        <v>0.4132773314989224</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.4449351694028761</v>
+        <v>0.405451195420384</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>0.3824491267042096</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.5001105314986991</v>
+        <v>0.4747917622903206</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.4732632252467629</v>
+        <v>0.4482704268390983</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>0.3203120814195544</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.4656046654836167</v>
+        <v>0.3997005162946713</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.4047862086542425</v>
+        <v>0.3870177826040014</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>0.2694313149282576</v>
@@ -741,31 +741,31 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.4413356370932798</v>
+        <v>0.3928905113032732</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.2885471850027521</v>
+        <v>0.2581762177825583</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.3290858686859495</v>
+        <v>0.3225422572098332</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.3232837334528474</v>
+        <v>0.2976203129174493</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.2219562012705778</v>
+        <v>0.1935928051222673</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.2588526802764488</v>
+        <v>0.2544315480598982</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.38532162251763</v>
+        <v>0.3481765574850554</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.2584147074998855</v>
+        <v>0.2295078115694208</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.2994217658549509</v>
+        <v>0.2934473894066592</v>
       </c>
     </row>
     <row r="8">
@@ -776,31 +776,31 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.3858842805109594</v>
+        <v>0.3396439430082163</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.2391233356538875</v>
+        <v>0.2162493728515869</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.246193737888675</v>
+        <v>0.2468260291698436</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.2711140029350211</v>
+        <v>0.2481260501129461</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.176444785929165</v>
+        <v>0.1538786674634725</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0.1718214153167061</v>
+        <v>0.1795157510754685</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0.3465328212126507</v>
+        <v>0.3111683145518659</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.2217433661989985</v>
+        <v>0.2010617234559971</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0.2402526915423759</v>
+        <v>0.2342790527430347</v>
       </c>
     </row>
     <row r="9">
@@ -811,31 +811,31 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.5029640080197219</v>
+        <v>0.4410919871254481</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.3469579138239481</v>
+        <v>0.308296415538077</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.4241578072760987</v>
+        <v>0.4181638057377529</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.3796787474390996</v>
+        <v>0.348037233982761</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.2720500525574621</v>
+        <v>0.2441935050590051</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.3524838755224422</v>
+        <v>0.3411971094773891</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0.4283103193327163</v>
+        <v>0.3856396188058301</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0.2950228232018943</v>
+        <v>0.2664679053589573</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0.3703137319397123</v>
+        <v>0.3560784962973363</v>
       </c>
     </row>
     <row r="10">
@@ -850,31 +850,31 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.2466533911207902</v>
+        <v>0.2434410228568307</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.2565376234083049</v>
+        <v>0.2409940306333904</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.2482736025567329</v>
+        <v>0.2326361868811115</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.2217395663786306</v>
+        <v>0.2142456501107638</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.09409214674039533</v>
+        <v>0.09263003690487182</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.1208374846351199</v>
+        <v>0.1276393480827268</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.2342895536819191</v>
+        <v>0.2289158214085625</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.1751828127629845</v>
+        <v>0.1661868289436737</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.1939773291547254</v>
+        <v>0.187182477123139</v>
       </c>
     </row>
     <row r="11">
@@ -885,31 +885,31 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.1898095282830959</v>
+        <v>0.1907223908377931</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.1997004141018087</v>
+        <v>0.191780472690145</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.1774091275086271</v>
+        <v>0.1645357281670542</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.1687353409103804</v>
+        <v>0.1548277565125789</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.05885226973465545</v>
+        <v>0.06228224287155674</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.06879504442816714</v>
+        <v>0.07375604251557186</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.1944908488942041</v>
+        <v>0.190034068998459</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.1411050766469618</v>
+        <v>0.1358130183699174</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.1451356893385952</v>
+        <v>0.1377312016829463</v>
       </c>
     </row>
     <row r="12">
@@ -920,31 +920,31 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.3160145068250873</v>
+        <v>0.3090506764256635</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.3167037037431532</v>
+        <v>0.2990647802735201</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.3340401987738181</v>
+        <v>0.3119519018980396</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.2826403069150239</v>
+        <v>0.2649879473738325</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.1380036699438708</v>
+        <v>0.1342748349630047</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.2002405892402433</v>
+        <v>0.2039772044199739</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.2819654539479931</v>
+        <v>0.2692514208372688</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.2176493818895979</v>
+        <v>0.2019844890877704</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0.2577918967984325</v>
+        <v>0.2391809210858375</v>
       </c>
     </row>
     <row r="13">
@@ -959,31 +959,31 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.080827249226728</v>
+        <v>0.07399163441914862</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.05823098592722193</v>
+        <v>0.0694514924124997</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.09441337617975107</v>
+        <v>0.0904011504941301</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.05319632420628293</v>
+        <v>0.06157290580377987</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.05689523942120527</v>
+        <v>0.04954421353677042</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.04249989293498888</v>
+        <v>0.04147029969009031</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.06723689362114714</v>
+        <v>0.06787159752048272</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.0575753420851997</v>
+        <v>0.05972142413707508</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.07085537596189626</v>
+        <v>0.06842568711204067</v>
       </c>
     </row>
     <row r="14">
@@ -994,31 +994,31 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.04984710812402083</v>
+        <v>0.04636799115582752</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.02975104541224738</v>
+        <v>0.03903763107413056</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.05262837504876525</v>
+        <v>0.04878902691420154</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.02530868218253929</v>
+        <v>0.03539419407378353</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.02945679381882823</v>
+        <v>0.02474417308268423</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0.01715058934460361</v>
+        <v>0.01623928865980547</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.0475329358675274</v>
+        <v>0.04798125771210714</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.03787212251384846</v>
+        <v>0.04054517777870456</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.04127432894051737</v>
+        <v>0.04248606343901008</v>
       </c>
     </row>
     <row r="15">
@@ -1029,31 +1029,31 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.1191241694933287</v>
+        <v>0.1107898403208788</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.0978388579936252</v>
+        <v>0.1119145426842672</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.1533677109060974</v>
+        <v>0.1506679314746833</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.09303268994320174</v>
+        <v>0.09923622256413969</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.09754602349237416</v>
+        <v>0.08404285300405875</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0.08986977284869249</v>
+        <v>0.08988587078104367</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.09298774795352301</v>
+        <v>0.09632105641957162</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.08527199601319911</v>
+        <v>0.08405054800135528</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.109892033086651</v>
+        <v>0.1081917348644771</v>
       </c>
     </row>
     <row r="16">
@@ -1068,31 +1068,31 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.2807150773981362</v>
+        <v>0.2584946618186473</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.2147325958129284</v>
+        <v>0.2026631501550434</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.199577453218781</v>
+        <v>0.1916390354652999</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.218121588944378</v>
+        <v>0.2102289689071407</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.1391908963230728</v>
+        <v>0.128250271495198</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0.1170031953429169</v>
+        <v>0.1187915259234743</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.2501080246998801</v>
+        <v>0.2349478947396191</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.1783443098308589</v>
+        <v>0.167118795285524</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.16288063728964</v>
+        <v>0.1592113937317494</v>
       </c>
     </row>
     <row r="17">
@@ -1103,31 +1103,31 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.2507700043450333</v>
+        <v>0.2308892092994714</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.1870940664698035</v>
+        <v>0.176747335080706</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.1610977255455545</v>
+        <v>0.1558067116395825</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.1890184602461841</v>
+        <v>0.1842705667851912</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.1175470932371663</v>
+        <v>0.10599752830818</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0.0877790334129884</v>
+        <v>0.08870829937120299</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.2285624377737537</v>
+        <v>0.214265771825843</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.159939460990371</v>
+        <v>0.1504129073899769</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.1398170843121347</v>
+        <v>0.136264711853671</v>
       </c>
     </row>
     <row r="18">
@@ -1138,31 +1138,31 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.3141416914663673</v>
+        <v>0.2887002357744994</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.2481324942288383</v>
+        <v>0.2290646092616782</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.2475552608383892</v>
+        <v>0.2365777460481445</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.2487304796293391</v>
+        <v>0.2393603117884866</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.1691366455307075</v>
+        <v>0.1502560382600164</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0.153483405076763</v>
+        <v>0.1557822107223183</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0.2729750716981049</v>
+        <v>0.2553922250896048</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0.1994719594363856</v>
+        <v>0.1855186742623794</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0.1967909768119987</v>
+        <v>0.1891680988468435</v>
       </c>
     </row>
     <row r="19">
@@ -1213,7 +1213,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido (tasa de respuesta: 71,23%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido (tasa de respuesta: 79,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1316,25 +1316,25 @@
         <v>14</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K4" s="6" t="n">
         <v>6</v>
@@ -1351,25 +1351,25 @@
         <v>9296</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>7265</v>
+        <v>7917</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>1069</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>11106</v>
+        <v>13629</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>8791</v>
+        <v>10235</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>1659</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>20403</v>
+        <v>22926</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>16056</v>
+        <v>18152</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>2728</v>
@@ -1383,28 +1383,28 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>5751</v>
+        <v>5536</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>3946</v>
+        <v>4624</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>264</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>7129</v>
+        <v>9514</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>5297</v>
+        <v>6570</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>253</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>15211</v>
+        <v>17446</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>10840</v>
+        <v>12446</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>1038</v>
@@ -1418,28 +1418,28 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>13983</v>
+        <v>14301</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>11413</v>
+        <v>12480</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>3012</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>15482</v>
+        <v>19562</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>13227</v>
+        <v>14280</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>4039</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>26672</v>
+        <v>30299</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>21696</v>
+        <v>24241</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>5519</v>
@@ -1457,31 +1457,31 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9">
@@ -1492,31 +1492,31 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>92073</v>
+        <v>101028</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>57478</v>
+        <v>64891</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>23017</v>
+        <v>23472</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>60896</v>
+        <v>67686</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>36542</v>
+        <v>38841</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>13238</v>
+        <v>13807</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>152969</v>
+        <v>168715</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>94019</v>
+        <v>103732</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>36255</v>
+        <v>37280</v>
       </c>
     </row>
     <row r="10">
@@ -1527,31 +1527,31 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>80505</v>
+        <v>87336</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>47633</v>
+        <v>54353</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>17219</v>
+        <v>17962</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>51069</v>
+        <v>56430</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>29049</v>
+        <v>30873</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>8787</v>
+        <v>9742</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>137570</v>
+        <v>150782</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>80677</v>
+        <v>90875</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>29091</v>
+        <v>29763</v>
       </c>
     </row>
     <row r="11">
@@ -1562,31 +1562,31 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>104930</v>
+        <v>113422</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>69113</v>
+        <v>77488</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>29666</v>
+        <v>30431</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>71519</v>
+        <v>79152</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>44789</v>
+        <v>48993</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>18027</v>
+        <v>18516</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>170035</v>
+        <v>186868</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>107338</v>
+        <v>120437</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>44839</v>
+        <v>45236</v>
       </c>
     </row>
     <row r="12">
@@ -1601,31 +1601,31 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>30</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
@@ -1636,31 +1636,31 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>33034</v>
+        <v>38411</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>39316</v>
+        <v>43423</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>23104</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>29257</v>
+        <v>33471</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>14467</v>
+        <v>16974</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>8348</v>
+        <v>9677</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>62292</v>
+        <v>71882</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>53783</v>
+        <v>60396</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>31451</v>
+        <v>32780</v>
       </c>
     </row>
     <row r="14">
@@ -1671,31 +1671,31 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>25421</v>
+        <v>30093</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>30605</v>
+        <v>34555</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>16509</v>
+        <v>16340</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>22264</v>
+        <v>24188</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>9049</v>
+        <v>11413</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>4752</v>
+        <v>5592</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>51710</v>
+        <v>59672</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>43321</v>
+        <v>49358</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>23532</v>
+        <v>24120</v>
       </c>
     </row>
     <row r="15">
@@ -1706,31 +1706,31 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>42324</v>
+        <v>48763</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>48537</v>
+        <v>53886</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>31085</v>
+        <v>30981</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>37293</v>
+        <v>41398</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>21219</v>
+        <v>24605</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>13833</v>
+        <v>15464</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>74967</v>
+        <v>84547</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>66821</v>
+        <v>73406</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>41798</v>
+        <v>41886</v>
       </c>
     </row>
     <row r="16">
@@ -1745,16 +1745,16 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>13</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>11</v>
@@ -1763,10 +1763,10 @@
         <v>6</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>19</v>
@@ -1780,16 +1780,16 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>12476</v>
+        <v>13048</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>8509</v>
+        <v>11751</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>11749</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>7948</v>
+        <v>10550</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>8014</v>
@@ -1798,10 +1798,10 @@
         <v>4394</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>20424</v>
+        <v>23597</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>16523</v>
+        <v>19765</v>
       </c>
       <c r="K17" s="6" t="n">
         <v>16143</v>
@@ -1815,31 +1815,31 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>7694</v>
+        <v>8176</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>4347</v>
+        <v>6605</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>6549</v>
+        <v>6341</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>3781</v>
+        <v>6064</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>4149</v>
+        <v>4003</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>1773</v>
+        <v>1721</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>14438</v>
+        <v>16682</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>10868</v>
+        <v>13419</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>9403</v>
+        <v>10023</v>
       </c>
     </row>
     <row r="19">
@@ -1850,31 +1850,31 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>18387</v>
+        <v>19537</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>14296</v>
+        <v>18935</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>19085</v>
+        <v>19581</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>13899</v>
+        <v>17003</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>13741</v>
+        <v>13595</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>9291</v>
+        <v>9524</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>28245</v>
+        <v>33488</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>24471</v>
+        <v>27817</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>25036</v>
+        <v>25524</v>
       </c>
     </row>
     <row r="20">
@@ -1889,31 +1889,31 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>366</v>
+        <v>406</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21">
@@ -1924,31 +1924,31 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>146880</v>
+        <v>161783</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>112567</v>
+        <v>127982</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>58938</v>
+        <v>59393</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>109207</v>
+        <v>125336</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>67814</v>
+        <v>74064</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>27638</v>
+        <v>29537</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>256087</v>
+        <v>287119</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>180381</v>
+        <v>202045</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>86577</v>
+        <v>88930</v>
       </c>
     </row>
     <row r="22">
@@ -1959,31 +1959,31 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>131211</v>
+        <v>144506</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>98079</v>
+        <v>111616</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>47575</v>
+        <v>48288</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>94636</v>
+        <v>109860</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>57269</v>
+        <v>61213</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>20735</v>
+        <v>22057</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>234026</v>
+        <v>261844</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>161766</v>
+        <v>181848</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>74318</v>
+        <v>76113</v>
       </c>
     </row>
     <row r="23">
@@ -1994,31 +1994,31 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>164370</v>
+        <v>180688</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>130076</v>
+        <v>144654</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>73107</v>
+        <v>73321</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>124532</v>
+        <v>142704</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>82403</v>
+        <v>86772</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>36256</v>
+        <v>38734</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>279500</v>
+        <v>312103</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>201750</v>
+        <v>224291</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>104601</v>
+        <v>105663</v>
       </c>
     </row>
     <row r="24">
